--- a/Result_Update_Layout.xlsx
+++ b/Result_Update_Layout.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="60">
   <si>
     <t>บริษัท โพนิซ จำกัด (สำนักงานใหญ่)</t>
   </si>
@@ -33,8 +33,8 @@
   </si>
   <si>
     <t xml:space="preserve">โปรเจค : โซลาร์เซลล์ 10k 1เฟส 
-      กำลังไฟสูงสุด ( 10.00kWp ) 
-      INVERTER : HUAWEI 
+          กำลังไฟสูงสุด ( 10.00kWp ) 
+          INVERTER : HUAWEI 
  วันที่ : 13 / 5 / 2568 
  เลขที่เอกสาร : PNMMA25016</t>
   </si>
@@ -69,10 +69,10 @@
     <t>Scope of Supply</t>
   </si>
   <si>
-    <t>cost per unit</t>
-  </si>
-  <si>
-    <t>total cost</t>
+    <t>PONIX</t>
+  </si>
+  <si>
+    <t>Cost</t>
   </si>
   <si>
     <t>A</t>
@@ -174,52 +174,117 @@
     <t>SUM B</t>
   </si>
   <si>
-    <t>เงื่อนไขการชำระเงิน</t>
-  </si>
-  <si>
-    <t>เงื่อนไขการรับประกัน</t>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Kanit Light"/>
+      </rPr>
+      <t xml:space="preserve">เงื่อนไขการชำระเงิน
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Kanit Light"/>
+      </rPr>
+      <t xml:space="preserve">1. มัดจำ 30%
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Kanit Light"/>
+      </rPr>
+      <t xml:space="preserve">2. ชำระ 70% ณ วันส่งมอบงาน
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Kanit Light"/>
+      </rPr>
+      <t xml:space="preserve">หมายเหตุ
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Kanit Light"/>
+      </rPr>
+      <t>ยืนยันราคา 30 วันนับแต่วันเสนอราคา</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Kanit Light"/>
+      </rPr>
+      <t xml:space="preserve">
+เงื่อนไขการรับประกัน
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Kanit Light"/>
+      </rPr>
+      <t xml:space="preserve">1. รับประกันระบบ 2 ปี
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Kanit Light"/>
+      </rPr>
+      <t xml:space="preserve">2. รับประกันอินเวอร์เตอร์ 10 ปี จากผู้ผลิต
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Kanit Light"/>
+      </rPr>
+      <t xml:space="preserve">3. รับประกันแผงโซลาร์เซลล์ 30 ปี จากผู้ผลิต
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Kanit Light"/>
+      </rPr>
+      <t xml:space="preserve">4. บริการหลังการติดตั้ง 3 ปี ปีละ 1 ครั้ง
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Kanit Light"/>
+      </rPr>
+      <t xml:space="preserve">5. Monitoring Service Free Lifetime
+</t>
+    </r>
   </si>
   <si>
     <t>รวม(Total)</t>
   </si>
   <si>
-    <t>1. มัดจำ 30%</t>
-  </si>
-  <si>
-    <t>1. รับประกันระบบ 2 ปี</t>
-  </si>
-  <si>
     <t>ส่วนลด(Discount)</t>
   </si>
   <si>
     <t>-</t>
   </si>
   <si>
-    <t>2. ชำระ 70% ณ วันส่งมอบงาน</t>
-  </si>
-  <si>
-    <t>2. รับประกันอินเวอร์เตอร์ 10 ปี จากผู้ผลิต</t>
-  </si>
-  <si>
-    <t>3. รับประกันแผงโซลาร์เซลล์ 30 ปี จากผู้ผลิต</t>
-  </si>
-  <si>
     <t>ภาษีมูลค่าเพิ่ม Vat7%</t>
   </si>
   <si>
-    <t>4. บริการหลังการติดตั้ง 3 ปี ปีละ 1 ครั้ง</t>
-  </si>
-  <si>
     <t>รวมเงินทั้งสิ้น (Grand Total)</t>
   </si>
   <si>
-    <t>หมายเหตุ</t>
-  </si>
-  <si>
-    <t>5. Monitoring Service Free Lifetime</t>
-  </si>
-  <si>
-    <t>ยืนยันราคา 30 วันนับแต่วันเสนอราคา</t>
+    <t>สองแสนสี่หมื่นสี่พันบาทถ้วน</t>
   </si>
   <si>
     <t xml:space="preserve">ลงชื่อผู้ให้บริการ
@@ -236,7 +301,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -245,7 +310,7 @@
       <name val="Calibri"/>
     </font>
     <font>
-      <sz val="10"/>
+      <sz val="9"/>
       <name val="Kanit Light"/>
     </font>
     <font>
@@ -264,12 +329,11 @@
       <name val="Kanit Light"/>
     </font>
     <font>
-      <sz val="8"/>
+      <sz val="10"/>
       <name val="Kanit Light"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
+      <sz val="9.5"/>
       <name val="Kanit Light"/>
     </font>
     <font>
@@ -277,8 +341,12 @@
       <sz val="10"/>
       <name val="Kanit Light"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Kanit Light"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -293,11 +361,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFBFBFBF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE2E2E2"/>
       </patternFill>
     </fill>
   </fills>
@@ -331,42 +394,52 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="4" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="bottom" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -707,7 +780,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K49"/>
+  <dimension ref="A1:K85"/>
   <sheetFormatPr defaultRowHeight="24.5" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="5" style="1" customWidth="1"/>
@@ -745,20 +818,20 @@
       <c r="K2" s="3"/>
     </row>
     <row r="3" ht="24.5" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C3" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="D3" s="4"/>
-      <c r="E3" s="4"/>
-      <c r="F3" s="4"/>
-      <c r="G3" s="4"/>
-      <c r="H3" s="4"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
       <c r="I3" s="3"/>
       <c r="J3" s="3"/>
       <c r="K3" s="3"/>
     </row>
     <row r="4" ht="24.5" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C4" s="4"/>
+      <c r="C4" s="4" t="s">
+        <v>2</v>
+      </c>
       <c r="D4" s="4"/>
       <c r="E4" s="4"/>
       <c r="F4" s="4"/>
@@ -801,51 +874,43 @@
       <c r="J7" s="3"/>
       <c r="K7" s="3"/>
     </row>
-    <row r="8" ht="24.5" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A8" s="5" t="s">
+    <row r="8" ht="24.5" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C8" s="4"/>
+      <c r="D8" s="4"/>
+      <c r="E8" s="4"/>
+      <c r="F8" s="4"/>
+      <c r="G8" s="4"/>
+      <c r="H8" s="4"/>
+      <c r="I8" s="3"/>
+      <c r="J8" s="3"/>
+      <c r="K8" s="3"/>
+    </row>
+    <row r="9" ht="24.5" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C9" s="4"/>
+      <c r="D9" s="4"/>
+      <c r="E9" s="4"/>
+      <c r="F9" s="4"/>
+      <c r="G9" s="4"/>
+      <c r="H9" s="4"/>
+      <c r="I9" s="3"/>
+      <c r="J9" s="3"/>
+      <c r="K9" s="3"/>
+    </row>
+    <row r="10" ht="24.5" customHeight="1" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C10" s="4"/>
+      <c r="D10" s="4"/>
+      <c r="E10" s="4"/>
+      <c r="F10" s="4"/>
+      <c r="G10" s="4"/>
+      <c r="H10" s="4"/>
+      <c r="I10" s="3"/>
+      <c r="J10" s="3"/>
+      <c r="K10" s="3"/>
+    </row>
+    <row r="11" ht="24.5" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A11" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="B8" s="5"/>
-      <c r="C8" s="5"/>
-      <c r="D8" s="5"/>
-      <c r="E8" s="5"/>
-      <c r="F8" s="5"/>
-      <c r="G8" s="5"/>
-      <c r="H8" s="5"/>
-      <c r="I8" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="J8" s="6"/>
-      <c r="K8" s="6"/>
-    </row>
-    <row r="9" ht="24.5" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A9" s="5"/>
-      <c r="B9" s="5"/>
-      <c r="C9" s="5"/>
-      <c r="D9" s="5"/>
-      <c r="E9" s="5"/>
-      <c r="F9" s="5"/>
-      <c r="G9" s="5"/>
-      <c r="H9" s="5"/>
-      <c r="I9" s="6"/>
-      <c r="J9" s="6"/>
-      <c r="K9" s="6"/>
-    </row>
-    <row r="10" ht="24.5" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A10" s="5"/>
-      <c r="B10" s="5"/>
-      <c r="C10" s="5"/>
-      <c r="D10" s="5"/>
-      <c r="E10" s="5"/>
-      <c r="F10" s="5"/>
-      <c r="G10" s="5"/>
-      <c r="H10" s="5"/>
-      <c r="I10" s="6"/>
-      <c r="J10" s="6"/>
-      <c r="K10" s="6"/>
-    </row>
-    <row r="11" ht="24.5" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A11" s="5"/>
       <c r="B11" s="5"/>
       <c r="C11" s="5"/>
       <c r="D11" s="5"/>
@@ -853,7 +918,9 @@
       <c r="F11" s="5"/>
       <c r="G11" s="5"/>
       <c r="H11" s="5"/>
-      <c r="I11" s="6"/>
+      <c r="I11" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="J11" s="6"/>
       <c r="K11" s="6"/>
     </row>
@@ -910,801 +977,1480 @@
       <c r="K15" s="6"/>
     </row>
     <row r="16" ht="24.5" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A16" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="B16" s="7"/>
-      <c r="C16" s="7"/>
-      <c r="D16" s="7"/>
-      <c r="E16" s="7"/>
-      <c r="F16" s="7"/>
-      <c r="G16" s="7"/>
-      <c r="H16" s="7"/>
-      <c r="I16" s="7"/>
-      <c r="J16" s="7"/>
-      <c r="K16" s="7"/>
+      <c r="A16" s="5"/>
+      <c r="B16" s="5"/>
+      <c r="C16" s="5"/>
+      <c r="D16" s="5"/>
+      <c r="E16" s="5"/>
+      <c r="F16" s="5"/>
+      <c r="G16" s="5"/>
+      <c r="H16" s="5"/>
+      <c r="I16" s="6"/>
+      <c r="J16" s="6"/>
+      <c r="K16" s="6"/>
     </row>
     <row r="17" ht="24.5" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A17" s="8" t="s">
+      <c r="A17" s="5"/>
+      <c r="B17" s="5"/>
+      <c r="C17" s="5"/>
+      <c r="D17" s="5"/>
+      <c r="E17" s="5"/>
+      <c r="F17" s="5"/>
+      <c r="G17" s="5"/>
+      <c r="H17" s="5"/>
+      <c r="I17" s="6"/>
+      <c r="J17" s="6"/>
+      <c r="K17" s="6"/>
+    </row>
+    <row r="18" ht="24.5" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A18" s="5"/>
+      <c r="B18" s="5"/>
+      <c r="C18" s="5"/>
+      <c r="D18" s="5"/>
+      <c r="E18" s="5"/>
+      <c r="F18" s="5"/>
+      <c r="G18" s="5"/>
+      <c r="H18" s="5"/>
+      <c r="I18" s="6"/>
+      <c r="J18" s="6"/>
+      <c r="K18" s="6"/>
+    </row>
+    <row r="19" ht="24.5" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A19" s="5"/>
+      <c r="B19" s="5"/>
+      <c r="C19" s="5"/>
+      <c r="D19" s="5"/>
+      <c r="E19" s="5"/>
+      <c r="F19" s="5"/>
+      <c r="G19" s="5"/>
+      <c r="H19" s="5"/>
+      <c r="I19" s="6"/>
+      <c r="J19" s="6"/>
+      <c r="K19" s="6"/>
+    </row>
+    <row r="20" ht="24.5" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A20" s="5"/>
+      <c r="B20" s="5"/>
+      <c r="C20" s="5"/>
+      <c r="D20" s="5"/>
+      <c r="E20" s="5"/>
+      <c r="F20" s="5"/>
+      <c r="G20" s="5"/>
+      <c r="H20" s="5"/>
+      <c r="I20" s="6"/>
+      <c r="J20" s="6"/>
+      <c r="K20" s="6"/>
+    </row>
+    <row r="21" ht="24.5" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A21" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B21" s="7"/>
+      <c r="C21" s="7"/>
+      <c r="D21" s="7"/>
+      <c r="E21" s="7"/>
+      <c r="F21" s="7"/>
+      <c r="G21" s="7"/>
+      <c r="H21" s="7"/>
+      <c r="I21" s="7"/>
+      <c r="J21" s="7"/>
+      <c r="K21" s="7"/>
+    </row>
+    <row r="22" ht="24.5" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A22" s="7"/>
+      <c r="B22" s="7"/>
+      <c r="C22" s="7"/>
+      <c r="D22" s="7"/>
+      <c r="E22" s="7"/>
+      <c r="F22" s="7"/>
+      <c r="G22" s="7"/>
+      <c r="H22" s="7"/>
+      <c r="I22" s="7"/>
+      <c r="J22" s="7"/>
+      <c r="K22" s="7"/>
+    </row>
+    <row r="23" ht="24.5" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A23" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="B17" s="8"/>
-      <c r="C17" s="8"/>
-      <c r="D17" s="8" t="s">
+      <c r="B23" s="8"/>
+      <c r="C23" s="8"/>
+      <c r="D23" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="E17" s="8" t="s">
+      <c r="E23" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="F17" s="8" t="s">
+      <c r="F23" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="G17" s="8" t="s">
+      <c r="G23" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="H17" s="8"/>
-      <c r="I17" s="8" t="s">
+      <c r="H23" s="8"/>
+      <c r="I23" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="J17" s="8"/>
-      <c r="K17" s="8" t="s">
+      <c r="J23" s="8"/>
+      <c r="K23" s="8" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="18" ht="24.5" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A18" s="8"/>
-      <c r="B18" s="8"/>
-      <c r="C18" s="8"/>
-      <c r="D18" s="8"/>
-      <c r="E18" s="8"/>
-      <c r="F18" s="8"/>
-      <c r="G18" s="8" t="s">
+    <row r="24" ht="24.5" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A24" s="8"/>
+      <c r="B24" s="8"/>
+      <c r="C24" s="8"/>
+      <c r="D24" s="8"/>
+      <c r="E24" s="8"/>
+      <c r="F24" s="8"/>
+      <c r="G24" s="8"/>
+      <c r="H24" s="8"/>
+      <c r="I24" s="8"/>
+      <c r="J24" s="8"/>
+      <c r="K24" s="8"/>
+    </row>
+    <row r="25" ht="24.5" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A25" s="8"/>
+      <c r="B25" s="8"/>
+      <c r="C25" s="8"/>
+      <c r="D25" s="8"/>
+      <c r="E25" s="8"/>
+      <c r="F25" s="8"/>
+      <c r="G25" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="H18" s="8"/>
-      <c r="I18" s="8" t="s">
+      <c r="H25" s="8"/>
+      <c r="I25" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="J18" s="8"/>
-      <c r="K18" s="8"/>
-    </row>
-    <row r="19" ht="24.5" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A19" s="8"/>
-      <c r="B19" s="8"/>
-      <c r="C19" s="8"/>
-      <c r="D19" s="8"/>
-      <c r="E19" s="8"/>
-      <c r="F19" s="8"/>
-      <c r="G19" s="8" t="s">
+      <c r="J25" s="8"/>
+      <c r="K25" s="8"/>
+    </row>
+    <row r="26" ht="24.5" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A26" s="8"/>
+      <c r="B26" s="8"/>
+      <c r="C26" s="8"/>
+      <c r="D26" s="8"/>
+      <c r="E26" s="8"/>
+      <c r="F26" s="8"/>
+      <c r="G26" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="H19" s="8" t="s">
+      <c r="H26" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="I19" s="8" t="s">
+      <c r="I26" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="J19" s="8" t="s">
+      <c r="J26" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="K19" s="8"/>
-    </row>
-    <row r="20" ht="24.5" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A20" s="9" t="s">
+      <c r="K26" s="8"/>
+    </row>
+    <row r="27" ht="24.5" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A27" s="8"/>
+      <c r="B27" s="8"/>
+      <c r="C27" s="8"/>
+      <c r="D27" s="8"/>
+      <c r="E27" s="8"/>
+      <c r="F27" s="8"/>
+      <c r="G27" s="8"/>
+      <c r="H27" s="8"/>
+      <c r="I27" s="8"/>
+      <c r="J27" s="8"/>
+      <c r="K27" s="8"/>
+    </row>
+    <row r="28" ht="24.5" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A28" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="B20" s="10" t="s">
+      <c r="B28" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="C20" s="10"/>
-      <c r="D20" s="11"/>
-      <c r="E20" s="11"/>
-      <c r="F20" s="11"/>
-      <c r="G20" s="11"/>
-      <c r="H20" s="11"/>
-      <c r="I20" s="11"/>
-      <c r="J20" s="11"/>
-      <c r="K20" s="11"/>
-    </row>
-    <row r="21" ht="24.5" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A21" s="12">
+      <c r="C28" s="10"/>
+      <c r="D28" s="11"/>
+      <c r="E28" s="11"/>
+      <c r="F28" s="11"/>
+      <c r="G28" s="11"/>
+      <c r="H28" s="11"/>
+      <c r="I28" s="11"/>
+      <c r="J28" s="11"/>
+      <c r="K28" s="11"/>
+    </row>
+    <row r="29" ht="24.5" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A29" s="9"/>
+      <c r="B29" s="10"/>
+      <c r="C29" s="10"/>
+      <c r="D29" s="11"/>
+      <c r="E29" s="11"/>
+      <c r="F29" s="11"/>
+      <c r="G29" s="11"/>
+      <c r="H29" s="11"/>
+      <c r="I29" s="11"/>
+      <c r="J29" s="11"/>
+      <c r="K29" s="11"/>
+    </row>
+    <row r="30" ht="24.5" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A30" s="12">
         <v>1</v>
       </c>
-      <c r="B21" s="13" t="s">
+      <c r="B30" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C21" s="13"/>
-      <c r="D21" s="12" t="s">
+      <c r="C30" s="13"/>
+      <c r="D30" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="E21" s="12">
+      <c r="E30" s="14">
         <v>16</v>
       </c>
-      <c r="F21" s="12" t="s">
+      <c r="F30" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="G21" s="14">
+      <c r="G30" s="15">
         <v>3000</v>
       </c>
-      <c r="H21" s="14">
+      <c r="H30" s="15">
         <v>48000</v>
       </c>
-      <c r="I21" s="14">
+      <c r="I30" s="15">
         <v>100</v>
       </c>
-      <c r="J21" s="14">
+      <c r="J30" s="15">
         <v>1600</v>
       </c>
-      <c r="K21" s="14">
+      <c r="K30" s="15">
         <v>49600</v>
       </c>
     </row>
-    <row r="22" ht="24.5" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A22" s="12">
-        <v>2</v>
-      </c>
-      <c r="B22" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="C22" s="13"/>
-      <c r="D22" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="E22" s="12">
-        <v>10000</v>
-      </c>
-      <c r="F22" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="G22" s="14">
-        <v>3</v>
-      </c>
-      <c r="H22" s="14">
-        <v>30000</v>
-      </c>
-      <c r="I22" s="14">
-        <v>1</v>
-      </c>
-      <c r="J22" s="14">
-        <v>10000</v>
-      </c>
-      <c r="K22" s="14">
-        <v>40000</v>
-      </c>
-    </row>
-    <row r="23" ht="24.5" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A23" s="12">
-        <v>3</v>
-      </c>
-      <c r="B23" s="13" t="s">
-        <v>25</v>
-      </c>
-      <c r="C23" s="13"/>
-      <c r="D23" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="E23" s="12">
-        <v>1</v>
-      </c>
-      <c r="F23" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="G23" s="14">
-        <v>49045</v>
-      </c>
-      <c r="H23" s="14">
-        <v>49045</v>
-      </c>
-      <c r="I23" s="14">
-        <v>12300</v>
-      </c>
-      <c r="J23" s="14">
-        <v>12300</v>
-      </c>
-      <c r="K23" s="14">
-        <v>61345</v>
-      </c>
-    </row>
-    <row r="24" ht="24.5" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A24" s="12">
-        <v>4</v>
-      </c>
-      <c r="B24" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="C24" s="13"/>
-      <c r="D24" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="E24" s="12">
-        <v>1</v>
-      </c>
-      <c r="F24" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="G24" s="14">
-        <v>3500</v>
-      </c>
-      <c r="H24" s="14">
-        <v>3500</v>
-      </c>
-      <c r="I24" s="14">
-        <v>1000</v>
-      </c>
-      <c r="J24" s="14">
-        <v>1000</v>
-      </c>
-      <c r="K24" s="14">
-        <v>4500</v>
-      </c>
-    </row>
-    <row r="25" ht="24.5" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A25" s="12">
-        <v>5</v>
-      </c>
-      <c r="B25" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="C25" s="13"/>
-      <c r="D25" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="E25" s="12">
-        <v>1</v>
-      </c>
-      <c r="F25" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="G25" s="14">
-        <v>7500</v>
-      </c>
-      <c r="H25" s="14">
-        <v>7500</v>
-      </c>
-      <c r="I25" s="14">
-        <v>2200</v>
-      </c>
-      <c r="J25" s="14">
-        <v>2200</v>
-      </c>
-      <c r="K25" s="14">
-        <v>9700</v>
-      </c>
-    </row>
-    <row r="26" ht="24.5" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A26" s="12">
-        <v>6</v>
-      </c>
-      <c r="B26" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="C26" s="13"/>
-      <c r="D26" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="E26" s="12">
-        <v>1</v>
-      </c>
-      <c r="F26" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="G26" s="14">
-        <v>4800</v>
-      </c>
-      <c r="H26" s="14">
-        <v>4800</v>
-      </c>
-      <c r="I26" s="14">
-        <v>1500</v>
-      </c>
-      <c r="J26" s="14">
-        <v>1500</v>
-      </c>
-      <c r="K26" s="14">
-        <v>6300</v>
-      </c>
-    </row>
-    <row r="27" ht="24.5" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A27" s="12">
-        <v>7</v>
-      </c>
-      <c r="B27" s="13" t="s">
-        <v>32</v>
-      </c>
-      <c r="C27" s="13"/>
-      <c r="D27" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="E27" s="12">
-        <v>200</v>
-      </c>
-      <c r="F27" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="G27" s="14">
-        <v>45</v>
-      </c>
-      <c r="H27" s="14">
-        <v>9000</v>
-      </c>
-      <c r="I27" s="14">
-        <v>15</v>
-      </c>
-      <c r="J27" s="14">
-        <v>3000</v>
-      </c>
-      <c r="K27" s="14">
-        <v>12000</v>
-      </c>
-    </row>
-    <row r="28" ht="24.5" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A28" s="12">
-        <v>8</v>
-      </c>
-      <c r="B28" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="C28" s="13"/>
-      <c r="D28" s="12" t="s">
-        <v>36</v>
-      </c>
-      <c r="E28" s="12">
-        <v>20</v>
-      </c>
-      <c r="F28" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="G28" s="14">
-        <v>250</v>
-      </c>
-      <c r="H28" s="14">
-        <v>5000</v>
-      </c>
-      <c r="I28" s="14">
-        <v>70</v>
-      </c>
-      <c r="J28" s="14">
-        <v>1400</v>
-      </c>
-      <c r="K28" s="14">
-        <v>6400</v>
-      </c>
-    </row>
-    <row r="29" ht="24.5" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A29" s="12">
-        <v>9</v>
-      </c>
-      <c r="B29" s="13" t="s">
-        <v>37</v>
-      </c>
-      <c r="C29" s="13"/>
-      <c r="D29" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="E29" s="12">
-        <v>20</v>
-      </c>
-      <c r="F29" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="G29" s="14">
-        <v>450</v>
-      </c>
-      <c r="H29" s="14">
-        <v>9000</v>
-      </c>
-      <c r="I29" s="14">
-        <v>100</v>
-      </c>
-      <c r="J29" s="14">
-        <v>2000</v>
-      </c>
-      <c r="K29" s="14">
-        <v>11000</v>
-      </c>
-    </row>
-    <row r="30" ht="24.5" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A30" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="B30" s="9"/>
-      <c r="C30" s="9"/>
-      <c r="D30" s="9"/>
-      <c r="E30" s="9"/>
-      <c r="F30" s="9"/>
-      <c r="G30" s="9"/>
-      <c r="H30" s="9"/>
-      <c r="I30" s="9"/>
-      <c r="J30" s="9"/>
-      <c r="K30" s="15">
-        <v>200845</v>
-      </c>
-    </row>
     <row r="31" ht="24.5" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A31" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="B31" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="C31" s="10"/>
-      <c r="D31" s="10"/>
-      <c r="E31" s="11"/>
-      <c r="F31" s="11"/>
-      <c r="G31" s="11"/>
-      <c r="H31" s="11"/>
-      <c r="I31" s="11"/>
-      <c r="J31" s="11"/>
-      <c r="K31" s="11"/>
+      <c r="A31" s="12"/>
+      <c r="B31" s="13"/>
+      <c r="C31" s="13"/>
+      <c r="D31" s="12"/>
+      <c r="E31" s="14"/>
+      <c r="F31" s="12"/>
+      <c r="G31" s="15"/>
+      <c r="H31" s="15"/>
+      <c r="I31" s="15"/>
+      <c r="J31" s="15"/>
+      <c r="K31" s="15"/>
     </row>
     <row r="32" ht="24.5" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" s="12">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="B32" s="13" t="s">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="C32" s="13"/>
-      <c r="D32" s="13"/>
-      <c r="E32" s="12">
+      <c r="D32" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="E32" s="14">
+        <v>10000</v>
+      </c>
+      <c r="F32" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="G32" s="15">
+        <v>3</v>
+      </c>
+      <c r="H32" s="15">
+        <v>30000</v>
+      </c>
+      <c r="I32" s="15">
         <v>1</v>
       </c>
-      <c r="F32" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="G32" s="14">
-        <v>0</v>
-      </c>
-      <c r="H32" s="14">
-        <v>0</v>
-      </c>
-      <c r="I32" s="14">
-        <v>0</v>
-      </c>
-      <c r="J32" s="14">
-        <v>0</v>
-      </c>
-      <c r="K32" s="14">
-        <v>3000</v>
+      <c r="J32" s="15">
+        <v>10000</v>
+      </c>
+      <c r="K32" s="15">
+        <v>40000</v>
       </c>
     </row>
     <row r="33" ht="24.5" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A33" s="12">
-        <v>11</v>
-      </c>
-      <c r="B33" s="13" t="s">
-        <v>44</v>
-      </c>
+      <c r="A33" s="12"/>
+      <c r="B33" s="13"/>
       <c r="C33" s="13"/>
-      <c r="D33" s="13"/>
-      <c r="E33" s="12">
-        <v>1</v>
-      </c>
-      <c r="F33" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="G33" s="14">
-        <v>0</v>
-      </c>
-      <c r="H33" s="14">
-        <v>0</v>
-      </c>
-      <c r="I33" s="14">
-        <v>0</v>
-      </c>
-      <c r="J33" s="14">
-        <v>0</v>
-      </c>
-      <c r="K33" s="14">
-        <v>3000</v>
-      </c>
+      <c r="D33" s="12"/>
+      <c r="E33" s="14"/>
+      <c r="F33" s="12"/>
+      <c r="G33" s="15"/>
+      <c r="H33" s="15"/>
+      <c r="I33" s="15"/>
+      <c r="J33" s="15"/>
+      <c r="K33" s="15"/>
     </row>
     <row r="34" ht="24.5" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" s="12">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="B34" s="13" t="s">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="C34" s="13"/>
-      <c r="D34" s="13"/>
-      <c r="E34" s="12">
+      <c r="D34" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="E34" s="14">
         <v>1</v>
       </c>
       <c r="F34" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="G34" s="14">
-        <v>0</v>
-      </c>
-      <c r="H34" s="14">
-        <v>0</v>
-      </c>
-      <c r="I34" s="14">
-        <v>0</v>
-      </c>
-      <c r="J34" s="14">
-        <v>0</v>
-      </c>
-      <c r="K34" s="14">
-        <v>3000</v>
+        <v>27</v>
+      </c>
+      <c r="G34" s="15">
+        <v>49045</v>
+      </c>
+      <c r="H34" s="15">
+        <v>49045</v>
+      </c>
+      <c r="I34" s="15">
+        <v>12300</v>
+      </c>
+      <c r="J34" s="15">
+        <v>12300</v>
+      </c>
+      <c r="K34" s="15">
+        <v>61345</v>
       </c>
     </row>
     <row r="35" ht="24.5" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A35" s="12">
-        <v>13</v>
-      </c>
-      <c r="B35" s="13" t="s">
-        <v>46</v>
-      </c>
+      <c r="A35" s="12"/>
+      <c r="B35" s="13"/>
       <c r="C35" s="13"/>
-      <c r="D35" s="13"/>
-      <c r="E35" s="12">
-        <v>1</v>
-      </c>
-      <c r="F35" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="G35" s="14">
-        <v>0</v>
-      </c>
-      <c r="H35" s="14">
-        <v>0</v>
-      </c>
-      <c r="I35" s="14">
-        <v>0</v>
-      </c>
-      <c r="J35" s="14">
-        <v>0</v>
-      </c>
-      <c r="K35" s="14">
-        <v>3000</v>
-      </c>
+      <c r="D35" s="12"/>
+      <c r="E35" s="14"/>
+      <c r="F35" s="12"/>
+      <c r="G35" s="15"/>
+      <c r="H35" s="15"/>
+      <c r="I35" s="15"/>
+      <c r="J35" s="15"/>
+      <c r="K35" s="15"/>
     </row>
     <row r="36" ht="24.5" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A36" s="12">
+        <v>4</v>
+      </c>
+      <c r="B36" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="C36" s="13"/>
+      <c r="D36" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="E36" s="14">
+        <v>1</v>
+      </c>
+      <c r="F36" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="G36" s="15">
+        <v>3500</v>
+      </c>
+      <c r="H36" s="15">
+        <v>3500</v>
+      </c>
+      <c r="I36" s="15">
+        <v>1000</v>
+      </c>
+      <c r="J36" s="15">
+        <v>1000</v>
+      </c>
+      <c r="K36" s="15">
+        <v>4500</v>
+      </c>
+    </row>
+    <row r="37" ht="24.5" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A37" s="12"/>
+      <c r="B37" s="13"/>
+      <c r="C37" s="13"/>
+      <c r="D37" s="12"/>
+      <c r="E37" s="14"/>
+      <c r="F37" s="12"/>
+      <c r="G37" s="15"/>
+      <c r="H37" s="15"/>
+      <c r="I37" s="15"/>
+      <c r="J37" s="15"/>
+      <c r="K37" s="15"/>
+    </row>
+    <row r="38" ht="24.5" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A38" s="12">
+        <v>5</v>
+      </c>
+      <c r="B38" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="C38" s="13"/>
+      <c r="D38" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="E38" s="14">
+        <v>1</v>
+      </c>
+      <c r="F38" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="G38" s="15">
+        <v>7500</v>
+      </c>
+      <c r="H38" s="15">
+        <v>7500</v>
+      </c>
+      <c r="I38" s="15">
+        <v>2200</v>
+      </c>
+      <c r="J38" s="15">
+        <v>2200</v>
+      </c>
+      <c r="K38" s="15">
+        <v>9700</v>
+      </c>
+    </row>
+    <row r="39" ht="24.5" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A39" s="12"/>
+      <c r="B39" s="13"/>
+      <c r="C39" s="13"/>
+      <c r="D39" s="12"/>
+      <c r="E39" s="14"/>
+      <c r="F39" s="12"/>
+      <c r="G39" s="15"/>
+      <c r="H39" s="15"/>
+      <c r="I39" s="15"/>
+      <c r="J39" s="15"/>
+      <c r="K39" s="15"/>
+    </row>
+    <row r="40" ht="24.5" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A40" s="12">
+        <v>6</v>
+      </c>
+      <c r="B40" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="C40" s="13"/>
+      <c r="D40" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="E40" s="14">
+        <v>1</v>
+      </c>
+      <c r="F40" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="G40" s="15">
+        <v>4800</v>
+      </c>
+      <c r="H40" s="15">
+        <v>4800</v>
+      </c>
+      <c r="I40" s="15">
+        <v>1500</v>
+      </c>
+      <c r="J40" s="15">
+        <v>1500</v>
+      </c>
+      <c r="K40" s="15">
+        <v>6300</v>
+      </c>
+    </row>
+    <row r="41" ht="24.5" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A41" s="12"/>
+      <c r="B41" s="13"/>
+      <c r="C41" s="13"/>
+      <c r="D41" s="12"/>
+      <c r="E41" s="14"/>
+      <c r="F41" s="12"/>
+      <c r="G41" s="15"/>
+      <c r="H41" s="15"/>
+      <c r="I41" s="15"/>
+      <c r="J41" s="15"/>
+      <c r="K41" s="15"/>
+    </row>
+    <row r="42" ht="24.5" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A42" s="12">
+        <v>7</v>
+      </c>
+      <c r="B42" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="C42" s="13"/>
+      <c r="D42" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="E42" s="14">
+        <v>200</v>
+      </c>
+      <c r="F42" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="G42" s="15">
+        <v>45</v>
+      </c>
+      <c r="H42" s="15">
+        <v>9000</v>
+      </c>
+      <c r="I42" s="15">
+        <v>15</v>
+      </c>
+      <c r="J42" s="15">
+        <v>3000</v>
+      </c>
+      <c r="K42" s="15">
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="43" ht="24.5" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A43" s="12"/>
+      <c r="B43" s="13"/>
+      <c r="C43" s="13"/>
+      <c r="D43" s="12"/>
+      <c r="E43" s="14"/>
+      <c r="F43" s="12"/>
+      <c r="G43" s="15"/>
+      <c r="H43" s="15"/>
+      <c r="I43" s="15"/>
+      <c r="J43" s="15"/>
+      <c r="K43" s="15"/>
+    </row>
+    <row r="44" ht="24.5" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A44" s="12">
+        <v>8</v>
+      </c>
+      <c r="B44" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="C44" s="13"/>
+      <c r="D44" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="E44" s="14">
+        <v>20</v>
+      </c>
+      <c r="F44" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="G44" s="15">
+        <v>250</v>
+      </c>
+      <c r="H44" s="15">
+        <v>5000</v>
+      </c>
+      <c r="I44" s="15">
+        <v>70</v>
+      </c>
+      <c r="J44" s="15">
+        <v>1400</v>
+      </c>
+      <c r="K44" s="15">
+        <v>6400</v>
+      </c>
+    </row>
+    <row r="45" ht="24.5" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A45" s="12"/>
+      <c r="B45" s="13"/>
+      <c r="C45" s="13"/>
+      <c r="D45" s="12"/>
+      <c r="E45" s="14"/>
+      <c r="F45" s="12"/>
+      <c r="G45" s="15"/>
+      <c r="H45" s="15"/>
+      <c r="I45" s="15"/>
+      <c r="J45" s="15"/>
+      <c r="K45" s="15"/>
+    </row>
+    <row r="46" ht="24.5" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A46" s="12">
+        <v>9</v>
+      </c>
+      <c r="B46" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="C46" s="13"/>
+      <c r="D46" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="E46" s="14">
+        <v>20</v>
+      </c>
+      <c r="F46" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="G46" s="15">
+        <v>450</v>
+      </c>
+      <c r="H46" s="15">
+        <v>9000</v>
+      </c>
+      <c r="I46" s="15">
+        <v>100</v>
+      </c>
+      <c r="J46" s="15">
+        <v>2000</v>
+      </c>
+      <c r="K46" s="15">
+        <v>11000</v>
+      </c>
+    </row>
+    <row r="47" ht="24.5" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A47" s="12"/>
+      <c r="B47" s="13"/>
+      <c r="C47" s="13"/>
+      <c r="D47" s="12"/>
+      <c r="E47" s="14"/>
+      <c r="F47" s="12"/>
+      <c r="G47" s="15"/>
+      <c r="H47" s="15"/>
+      <c r="I47" s="15"/>
+      <c r="J47" s="15"/>
+      <c r="K47" s="15"/>
+    </row>
+    <row r="48" ht="24.5" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A48" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="B48" s="9"/>
+      <c r="C48" s="9"/>
+      <c r="D48" s="9"/>
+      <c r="E48" s="9"/>
+      <c r="F48" s="9"/>
+      <c r="G48" s="9"/>
+      <c r="H48" s="9"/>
+      <c r="I48" s="9"/>
+      <c r="J48" s="9"/>
+      <c r="K48" s="16">
+        <v>200845</v>
+      </c>
+    </row>
+    <row r="49" ht="24.5" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A49" s="9"/>
+      <c r="B49" s="9"/>
+      <c r="C49" s="9"/>
+      <c r="D49" s="9"/>
+      <c r="E49" s="9"/>
+      <c r="F49" s="9"/>
+      <c r="G49" s="9"/>
+      <c r="H49" s="9"/>
+      <c r="I49" s="9"/>
+      <c r="J49" s="9"/>
+      <c r="K49" s="16"/>
+    </row>
+    <row r="50" ht="24.5" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A50" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="B50" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="C50" s="10"/>
+      <c r="D50" s="10"/>
+      <c r="E50" s="11"/>
+      <c r="F50" s="11"/>
+      <c r="G50" s="11"/>
+      <c r="H50" s="11"/>
+      <c r="I50" s="11"/>
+      <c r="J50" s="11"/>
+      <c r="K50" s="11"/>
+    </row>
+    <row r="51" ht="24.5" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A51" s="9"/>
+      <c r="B51" s="10"/>
+      <c r="C51" s="10"/>
+      <c r="D51" s="10"/>
+      <c r="E51" s="11"/>
+      <c r="F51" s="11"/>
+      <c r="G51" s="11"/>
+      <c r="H51" s="11"/>
+      <c r="I51" s="11"/>
+      <c r="J51" s="11"/>
+      <c r="K51" s="11"/>
+    </row>
+    <row r="52" ht="24.5" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A52" s="12">
+        <v>10</v>
+      </c>
+      <c r="B52" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="C52" s="13"/>
+      <c r="D52" s="13"/>
+      <c r="E52" s="14">
+        <v>1</v>
+      </c>
+      <c r="F52" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="G52" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="H52" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="I52" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="J52" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="K52" s="15">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="53" ht="24.5" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A53" s="12"/>
+      <c r="B53" s="13"/>
+      <c r="C53" s="13"/>
+      <c r="D53" s="13"/>
+      <c r="E53" s="14"/>
+      <c r="F53" s="12"/>
+      <c r="G53" s="15"/>
+      <c r="H53" s="15"/>
+      <c r="I53" s="15"/>
+      <c r="J53" s="15"/>
+      <c r="K53" s="15"/>
+    </row>
+    <row r="54" ht="24.5" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A54" s="12">
+        <v>11</v>
+      </c>
+      <c r="B54" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="C54" s="13"/>
+      <c r="D54" s="13"/>
+      <c r="E54" s="14">
+        <v>1</v>
+      </c>
+      <c r="F54" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="G54" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="H54" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="I54" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="J54" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="K54" s="15">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="55" ht="24.5" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A55" s="12"/>
+      <c r="B55" s="13"/>
+      <c r="C55" s="13"/>
+      <c r="D55" s="13"/>
+      <c r="E55" s="14"/>
+      <c r="F55" s="12"/>
+      <c r="G55" s="15"/>
+      <c r="H55" s="15"/>
+      <c r="I55" s="15"/>
+      <c r="J55" s="15"/>
+      <c r="K55" s="15"/>
+    </row>
+    <row r="56" ht="24.5" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A56" s="12">
+        <v>12</v>
+      </c>
+      <c r="B56" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="C56" s="13"/>
+      <c r="D56" s="13"/>
+      <c r="E56" s="14">
+        <v>1</v>
+      </c>
+      <c r="F56" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="G56" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="H56" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="I56" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="J56" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="K56" s="15">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="57" ht="24.5" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A57" s="12"/>
+      <c r="B57" s="13"/>
+      <c r="C57" s="13"/>
+      <c r="D57" s="13"/>
+      <c r="E57" s="14"/>
+      <c r="F57" s="12"/>
+      <c r="G57" s="15"/>
+      <c r="H57" s="15"/>
+      <c r="I57" s="15"/>
+      <c r="J57" s="15"/>
+      <c r="K57" s="15"/>
+    </row>
+    <row r="58" ht="24.5" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A58" s="12">
+        <v>13</v>
+      </c>
+      <c r="B58" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="C58" s="13"/>
+      <c r="D58" s="13"/>
+      <c r="E58" s="14">
+        <v>1</v>
+      </c>
+      <c r="F58" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="G58" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="H58" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="I58" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="J58" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="K58" s="15">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="59" ht="24.5" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A59" s="12"/>
+      <c r="B59" s="13"/>
+      <c r="C59" s="13"/>
+      <c r="D59" s="13"/>
+      <c r="E59" s="14"/>
+      <c r="F59" s="12"/>
+      <c r="G59" s="15"/>
+      <c r="H59" s="15"/>
+      <c r="I59" s="15"/>
+      <c r="J59" s="15"/>
+      <c r="K59" s="15"/>
+    </row>
+    <row r="60" ht="24.5" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A60" s="12">
         <v>14</v>
       </c>
-      <c r="B36" s="13" t="s">
+      <c r="B60" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="C36" s="13"/>
-      <c r="D36" s="13"/>
-      <c r="E36" s="12">
+      <c r="C60" s="13"/>
+      <c r="D60" s="13"/>
+      <c r="E60" s="14">
         <v>1</v>
       </c>
-      <c r="F36" s="12" t="s">
+      <c r="F60" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="G36" s="14">
-        <v>0</v>
-      </c>
-      <c r="H36" s="14">
-        <v>0</v>
-      </c>
-      <c r="I36" s="14">
-        <v>0</v>
-      </c>
-      <c r="J36" s="14">
-        <v>0</v>
-      </c>
-      <c r="K36" s="14">
+      <c r="G60" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="H60" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="I60" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="J60" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="K60" s="15">
         <v>3000</v>
       </c>
     </row>
-    <row r="37" ht="24.5" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A37" s="12">
+    <row r="61" ht="24.5" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A61" s="12"/>
+      <c r="B61" s="13"/>
+      <c r="C61" s="13"/>
+      <c r="D61" s="13"/>
+      <c r="E61" s="14"/>
+      <c r="F61" s="12"/>
+      <c r="G61" s="15"/>
+      <c r="H61" s="15"/>
+      <c r="I61" s="15"/>
+      <c r="J61" s="15"/>
+      <c r="K61" s="15"/>
+    </row>
+    <row r="62" ht="24.5" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A62" s="12">
         <v>15</v>
       </c>
-      <c r="B37" s="13" t="s">
+      <c r="B62" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="C37" s="13"/>
-      <c r="D37" s="13"/>
-      <c r="E37" s="12">
+      <c r="C62" s="13"/>
+      <c r="D62" s="13"/>
+      <c r="E62" s="14">
         <v>1</v>
       </c>
-      <c r="F37" s="12" t="s">
+      <c r="F62" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="G37" s="14">
-        <v>0</v>
-      </c>
-      <c r="H37" s="14">
-        <v>0</v>
-      </c>
-      <c r="I37" s="14">
-        <v>0</v>
-      </c>
-      <c r="J37" s="14">
-        <v>0</v>
-      </c>
-      <c r="K37" s="14">
+      <c r="G62" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="H62" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="I62" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="J62" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="K62" s="15">
         <v>12192.38</v>
       </c>
     </row>
-    <row r="38" ht="24.5" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A38" s="9" t="s">
+    <row r="63" ht="24.5" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A63" s="12"/>
+      <c r="B63" s="13"/>
+      <c r="C63" s="13"/>
+      <c r="D63" s="13"/>
+      <c r="E63" s="14"/>
+      <c r="F63" s="12"/>
+      <c r="G63" s="15"/>
+      <c r="H63" s="15"/>
+      <c r="I63" s="15"/>
+      <c r="J63" s="15"/>
+      <c r="K63" s="15"/>
+    </row>
+    <row r="64" ht="24.5" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A64" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="B38" s="9"/>
-      <c r="C38" s="9"/>
-      <c r="D38" s="9"/>
-      <c r="E38" s="9"/>
-      <c r="F38" s="9"/>
-      <c r="G38" s="9"/>
-      <c r="H38" s="9"/>
-      <c r="I38" s="9"/>
-      <c r="J38" s="9"/>
-      <c r="K38" s="15">
+      <c r="B64" s="9"/>
+      <c r="C64" s="9"/>
+      <c r="D64" s="9"/>
+      <c r="E64" s="9"/>
+      <c r="F64" s="9"/>
+      <c r="G64" s="9"/>
+      <c r="H64" s="9"/>
+      <c r="I64" s="9"/>
+      <c r="J64" s="9"/>
+      <c r="K64" s="16">
         <v>27192.379999999997</v>
       </c>
     </row>
-    <row r="39" ht="24.5" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A39" s="16" t="s">
+    <row r="65" ht="24.5" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A65" s="9"/>
+      <c r="B65" s="9"/>
+      <c r="C65" s="9"/>
+      <c r="D65" s="9"/>
+      <c r="E65" s="9"/>
+      <c r="F65" s="9"/>
+      <c r="G65" s="9"/>
+      <c r="H65" s="9"/>
+      <c r="I65" s="9"/>
+      <c r="J65" s="9"/>
+      <c r="K65" s="16"/>
+    </row>
+    <row r="66" ht="24.5" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A66" s="17" t="s">
         <v>50</v>
       </c>
-      <c r="E39" s="16" t="s">
+      <c r="B66" s="17"/>
+      <c r="C66" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="I39" s="17" t="s">
+      <c r="D66" s="17"/>
+      <c r="E66" s="17"/>
+      <c r="F66" s="17"/>
+      <c r="G66" s="17"/>
+      <c r="H66" s="17"/>
+      <c r="I66" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="J39" s="17"/>
-      <c r="K39" s="18">
+      <c r="J66" s="18"/>
+      <c r="K66" s="16">
         <v>228037.38</v>
       </c>
     </row>
-    <row r="40" ht="24.5" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A40" s="1" t="s">
+    <row r="67" ht="24.5" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A67" s="17"/>
+      <c r="B67" s="17"/>
+      <c r="C67" s="17"/>
+      <c r="D67" s="17"/>
+      <c r="E67" s="17"/>
+      <c r="F67" s="17"/>
+      <c r="G67" s="17"/>
+      <c r="H67" s="17"/>
+      <c r="I67" s="18"/>
+      <c r="J67" s="18"/>
+      <c r="K67" s="16"/>
+    </row>
+    <row r="68" ht="24.5" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A68" s="17"/>
+      <c r="B68" s="17"/>
+      <c r="C68" s="17"/>
+      <c r="D68" s="17"/>
+      <c r="E68" s="17"/>
+      <c r="F68" s="17"/>
+      <c r="G68" s="17"/>
+      <c r="H68" s="17"/>
+      <c r="I68" s="18" t="s">
         <v>53</v>
       </c>
-      <c r="E40" s="1" t="s">
+      <c r="J68" s="18"/>
+      <c r="K68" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="I40" s="17" t="s">
+    </row>
+    <row r="69" ht="24.5" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A69" s="17"/>
+      <c r="B69" s="17"/>
+      <c r="C69" s="17"/>
+      <c r="D69" s="17"/>
+      <c r="E69" s="17"/>
+      <c r="F69" s="17"/>
+      <c r="G69" s="17"/>
+      <c r="H69" s="17"/>
+      <c r="I69" s="18"/>
+      <c r="J69" s="18"/>
+      <c r="K69" s="16"/>
+    </row>
+    <row r="70" ht="24.5" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A70" s="17"/>
+      <c r="B70" s="17"/>
+      <c r="C70" s="17"/>
+      <c r="D70" s="17"/>
+      <c r="E70" s="17"/>
+      <c r="F70" s="17"/>
+      <c r="G70" s="17"/>
+      <c r="H70" s="17"/>
+      <c r="I70" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="J70" s="18"/>
+      <c r="K70" s="16">
+        <v>228037.38</v>
+      </c>
+    </row>
+    <row r="71" ht="24.5" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A71" s="17"/>
+      <c r="B71" s="17"/>
+      <c r="C71" s="17"/>
+      <c r="D71" s="17"/>
+      <c r="E71" s="17"/>
+      <c r="F71" s="17"/>
+      <c r="G71" s="17"/>
+      <c r="H71" s="17"/>
+      <c r="I71" s="18"/>
+      <c r="J71" s="18"/>
+      <c r="K71" s="16"/>
+    </row>
+    <row r="72" ht="24.5" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A72" s="17"/>
+      <c r="B72" s="17"/>
+      <c r="C72" s="17"/>
+      <c r="D72" s="17"/>
+      <c r="E72" s="17"/>
+      <c r="F72" s="17"/>
+      <c r="G72" s="17"/>
+      <c r="H72" s="17"/>
+      <c r="I72" s="18" t="s">
         <v>55</v>
       </c>
-      <c r="J40" s="17"/>
-      <c r="K40" s="18" t="s">
+      <c r="J72" s="18"/>
+      <c r="K72" s="16">
+        <v>15962.616600000001</v>
+      </c>
+    </row>
+    <row r="73" ht="24.5" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A73" s="17"/>
+      <c r="B73" s="17"/>
+      <c r="C73" s="17"/>
+      <c r="D73" s="17"/>
+      <c r="E73" s="17"/>
+      <c r="F73" s="17"/>
+      <c r="G73" s="17"/>
+      <c r="H73" s="17"/>
+      <c r="I73" s="18"/>
+      <c r="J73" s="18"/>
+      <c r="K73" s="16"/>
+    </row>
+    <row r="74" ht="24.5" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A74" s="17"/>
+      <c r="B74" s="17"/>
+      <c r="C74" s="17"/>
+      <c r="D74" s="17"/>
+      <c r="E74" s="17"/>
+      <c r="F74" s="17"/>
+      <c r="G74" s="17"/>
+      <c r="H74" s="17"/>
+      <c r="I74" s="18" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="41" ht="24.5" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A41" s="1" t="s">
+      <c r="J74" s="18"/>
+      <c r="K74" s="16">
+        <v>243999.9966</v>
+      </c>
+    </row>
+    <row r="75" ht="24.5" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A75" s="17"/>
+      <c r="B75" s="17"/>
+      <c r="C75" s="17"/>
+      <c r="D75" s="17"/>
+      <c r="E75" s="17"/>
+      <c r="F75" s="17"/>
+      <c r="G75" s="17"/>
+      <c r="H75" s="17"/>
+      <c r="I75" s="18"/>
+      <c r="J75" s="18"/>
+      <c r="K75" s="16"/>
+    </row>
+    <row r="76" ht="24.5" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A76" s="19" t="s">
         <v>57</v>
       </c>
-      <c r="E41" s="1" t="s">
+      <c r="B76" s="19"/>
+      <c r="C76" s="19"/>
+      <c r="D76" s="19"/>
+      <c r="E76" s="19"/>
+      <c r="F76" s="19"/>
+      <c r="G76" s="19"/>
+      <c r="H76" s="19"/>
+      <c r="I76" s="19"/>
+      <c r="J76" s="19"/>
+      <c r="K76" s="19"/>
+    </row>
+    <row r="77" ht="24.5" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A77" s="19"/>
+      <c r="B77" s="19"/>
+      <c r="C77" s="19"/>
+      <c r="D77" s="19"/>
+      <c r="E77" s="19"/>
+      <c r="F77" s="19"/>
+      <c r="G77" s="19"/>
+      <c r="H77" s="19"/>
+      <c r="I77" s="19"/>
+      <c r="J77" s="19"/>
+      <c r="K77" s="19"/>
+    </row>
+    <row r="78" ht="24.5" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A78" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="I41" s="17" t="s">
-        <v>52</v>
-      </c>
-      <c r="J41" s="17"/>
-      <c r="K41" s="18">
-        <v>228037.38</v>
-      </c>
-    </row>
-    <row r="42" ht="24.5" customHeight="1" spans="5:11" x14ac:dyDescent="0.25">
-      <c r="E42" s="1" t="s">
+      <c r="B78" s="8"/>
+      <c r="C78" s="8"/>
+      <c r="D78" s="8"/>
+      <c r="E78" s="8"/>
+      <c r="F78" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="I42" s="17" t="s">
-        <v>60</v>
-      </c>
-      <c r="J42" s="17"/>
-      <c r="K42" s="18">
-        <v>15962.616600000001</v>
-      </c>
-    </row>
-    <row r="43" ht="24.5" customHeight="1" spans="5:11" x14ac:dyDescent="0.25">
-      <c r="E43" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="I43" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="K43" s="1">
-        <v>243999.9966</v>
-      </c>
-    </row>
-    <row r="44" ht="24.5" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A44" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="E44" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="45" ht="24.5" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A45" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="B45" s="19" t="s">
-        <v>66</v>
-      </c>
-      <c r="C45" s="19"/>
-      <c r="D45" s="19"/>
-      <c r="H45" s="19" t="s">
-        <v>67</v>
-      </c>
-      <c r="I45" s="19"/>
-      <c r="J45" s="19"/>
-    </row>
-    <row r="46" ht="24.5" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B46" s="19"/>
-      <c r="C46" s="19"/>
-      <c r="D46" s="19"/>
-      <c r="H46" s="19"/>
-      <c r="I46" s="19"/>
-      <c r="J46" s="19"/>
-    </row>
-    <row r="47" ht="24.5" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B47" s="19"/>
-      <c r="C47" s="19"/>
-      <c r="D47" s="19"/>
-      <c r="H47" s="19"/>
-      <c r="I47" s="19"/>
-      <c r="J47" s="19"/>
-    </row>
-    <row r="48" ht="24.5" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B48" s="19"/>
-      <c r="C48" s="19"/>
-      <c r="D48" s="19"/>
-      <c r="H48" s="19"/>
-      <c r="I48" s="19"/>
-      <c r="J48" s="19"/>
-    </row>
-    <row r="49" ht="24.5" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B49" s="19"/>
-      <c r="C49" s="19"/>
-      <c r="D49" s="19"/>
-      <c r="H49" s="19"/>
-      <c r="I49" s="19"/>
-      <c r="J49" s="19"/>
+      <c r="G78" s="8"/>
+      <c r="H78" s="8"/>
+      <c r="I78" s="8"/>
+      <c r="J78" s="8"/>
+      <c r="K78" s="8"/>
+    </row>
+    <row r="79" ht="24.5" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A79" s="8"/>
+      <c r="B79" s="8"/>
+      <c r="C79" s="8"/>
+      <c r="D79" s="8"/>
+      <c r="E79" s="8"/>
+      <c r="F79" s="8"/>
+      <c r="G79" s="8"/>
+      <c r="H79" s="8"/>
+      <c r="I79" s="8"/>
+      <c r="J79" s="8"/>
+      <c r="K79" s="8"/>
+    </row>
+    <row r="80" ht="24.5" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A80" s="8"/>
+      <c r="B80" s="8"/>
+      <c r="C80" s="8"/>
+      <c r="D80" s="8"/>
+      <c r="E80" s="8"/>
+      <c r="F80" s="8"/>
+      <c r="G80" s="8"/>
+      <c r="H80" s="8"/>
+      <c r="I80" s="8"/>
+      <c r="J80" s="8"/>
+      <c r="K80" s="8"/>
+    </row>
+    <row r="81" ht="24.5" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A81" s="8"/>
+      <c r="B81" s="8"/>
+      <c r="C81" s="8"/>
+      <c r="D81" s="8"/>
+      <c r="E81" s="8"/>
+      <c r="F81" s="8"/>
+      <c r="G81" s="8"/>
+      <c r="H81" s="8"/>
+      <c r="I81" s="8"/>
+      <c r="J81" s="8"/>
+      <c r="K81" s="8"/>
+    </row>
+    <row r="82" ht="24.5" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A82" s="8"/>
+      <c r="B82" s="8"/>
+      <c r="C82" s="8"/>
+      <c r="D82" s="8"/>
+      <c r="E82" s="8"/>
+      <c r="F82" s="8"/>
+      <c r="G82" s="8"/>
+      <c r="H82" s="8"/>
+      <c r="I82" s="8"/>
+      <c r="J82" s="8"/>
+      <c r="K82" s="8"/>
+    </row>
+    <row r="83" ht="24.5" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A83" s="8"/>
+      <c r="B83" s="8"/>
+      <c r="C83" s="8"/>
+      <c r="D83" s="8"/>
+      <c r="E83" s="8"/>
+      <c r="F83" s="8"/>
+      <c r="G83" s="8"/>
+      <c r="H83" s="8"/>
+      <c r="I83" s="8"/>
+      <c r="J83" s="8"/>
+      <c r="K83" s="8"/>
+    </row>
+    <row r="84" ht="24.5" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A84" s="8"/>
+      <c r="B84" s="8"/>
+      <c r="C84" s="8"/>
+      <c r="D84" s="8"/>
+      <c r="E84" s="8"/>
+      <c r="F84" s="8"/>
+      <c r="G84" s="8"/>
+      <c r="H84" s="8"/>
+      <c r="I84" s="8"/>
+      <c r="J84" s="8"/>
+      <c r="K84" s="8"/>
+    </row>
+    <row r="85" ht="24.5" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A85" s="8"/>
+      <c r="B85" s="8"/>
+      <c r="C85" s="8"/>
+      <c r="D85" s="8"/>
+      <c r="E85" s="8"/>
+      <c r="F85" s="8"/>
+      <c r="G85" s="8"/>
+      <c r="H85" s="8"/>
+      <c r="I85" s="8"/>
+      <c r="J85" s="8"/>
+      <c r="K85" s="8"/>
     </row>
   </sheetData>
-  <mergeCells count="40">
-    <mergeCell ref="C1:H2"/>
-    <mergeCell ref="I1:K7"/>
-    <mergeCell ref="C3:H7"/>
-    <mergeCell ref="A8:H15"/>
-    <mergeCell ref="I8:K15"/>
-    <mergeCell ref="A16:K16"/>
-    <mergeCell ref="A17:C19"/>
-    <mergeCell ref="G17:H17"/>
-    <mergeCell ref="I17:J17"/>
-    <mergeCell ref="D17:D19"/>
-    <mergeCell ref="E17:E19"/>
-    <mergeCell ref="F17:F19"/>
-    <mergeCell ref="G18:H18"/>
-    <mergeCell ref="I18:J18"/>
-    <mergeCell ref="K17:K19"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="A30:J30"/>
-    <mergeCell ref="B31:D31"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="B33:D33"/>
-    <mergeCell ref="B34:D34"/>
-    <mergeCell ref="B35:D35"/>
-    <mergeCell ref="B36:D36"/>
-    <mergeCell ref="B37:D37"/>
-    <mergeCell ref="A38:J38"/>
-    <mergeCell ref="I39:J39"/>
-    <mergeCell ref="I40:J40"/>
-    <mergeCell ref="I41:J41"/>
-    <mergeCell ref="I42:J42"/>
-    <mergeCell ref="B45:D49"/>
-    <mergeCell ref="H45:J49"/>
+  <mergeCells count="201">
+    <mergeCell ref="C1:H3"/>
+    <mergeCell ref="I1:K10"/>
+    <mergeCell ref="C4:H10"/>
+    <mergeCell ref="A11:H20"/>
+    <mergeCell ref="I11:K20"/>
+    <mergeCell ref="A21:K22"/>
+    <mergeCell ref="A23:C27"/>
+    <mergeCell ref="G23:H24"/>
+    <mergeCell ref="I23:J24"/>
+    <mergeCell ref="D23:D27"/>
+    <mergeCell ref="E23:E27"/>
+    <mergeCell ref="F23:F27"/>
+    <mergeCell ref="K23:K27"/>
+    <mergeCell ref="G25:H25"/>
+    <mergeCell ref="I25:J25"/>
+    <mergeCell ref="G26:G27"/>
+    <mergeCell ref="H26:H27"/>
+    <mergeCell ref="I26:I27"/>
+    <mergeCell ref="J26:J27"/>
+    <mergeCell ref="B28:C29"/>
+    <mergeCell ref="A28:A29"/>
+    <mergeCell ref="D28:D29"/>
+    <mergeCell ref="E28:E29"/>
+    <mergeCell ref="F28:F29"/>
+    <mergeCell ref="G28:G29"/>
+    <mergeCell ref="H28:H29"/>
+    <mergeCell ref="I28:I29"/>
+    <mergeCell ref="J28:J29"/>
+    <mergeCell ref="K28:K29"/>
+    <mergeCell ref="B30:C31"/>
+    <mergeCell ref="A30:A31"/>
+    <mergeCell ref="D30:D31"/>
+    <mergeCell ref="E30:E31"/>
+    <mergeCell ref="F30:F31"/>
+    <mergeCell ref="G30:G31"/>
+    <mergeCell ref="H30:H31"/>
+    <mergeCell ref="I30:I31"/>
+    <mergeCell ref="J30:J31"/>
+    <mergeCell ref="K30:K31"/>
+    <mergeCell ref="B32:C33"/>
+    <mergeCell ref="A32:A33"/>
+    <mergeCell ref="D32:D33"/>
+    <mergeCell ref="E32:E33"/>
+    <mergeCell ref="F32:F33"/>
+    <mergeCell ref="G32:G33"/>
+    <mergeCell ref="H32:H33"/>
+    <mergeCell ref="I32:I33"/>
+    <mergeCell ref="J32:J33"/>
+    <mergeCell ref="K32:K33"/>
+    <mergeCell ref="B34:C35"/>
+    <mergeCell ref="A34:A35"/>
+    <mergeCell ref="D34:D35"/>
+    <mergeCell ref="E34:E35"/>
+    <mergeCell ref="F34:F35"/>
+    <mergeCell ref="G34:G35"/>
+    <mergeCell ref="H34:H35"/>
+    <mergeCell ref="I34:I35"/>
+    <mergeCell ref="J34:J35"/>
+    <mergeCell ref="K34:K35"/>
+    <mergeCell ref="B36:C37"/>
+    <mergeCell ref="A36:A37"/>
+    <mergeCell ref="D36:D37"/>
+    <mergeCell ref="E36:E37"/>
+    <mergeCell ref="F36:F37"/>
+    <mergeCell ref="G36:G37"/>
+    <mergeCell ref="H36:H37"/>
+    <mergeCell ref="I36:I37"/>
+    <mergeCell ref="J36:J37"/>
+    <mergeCell ref="K36:K37"/>
+    <mergeCell ref="B38:C39"/>
+    <mergeCell ref="A38:A39"/>
+    <mergeCell ref="D38:D39"/>
+    <mergeCell ref="E38:E39"/>
+    <mergeCell ref="F38:F39"/>
+    <mergeCell ref="G38:G39"/>
+    <mergeCell ref="H38:H39"/>
+    <mergeCell ref="I38:I39"/>
+    <mergeCell ref="J38:J39"/>
+    <mergeCell ref="K38:K39"/>
+    <mergeCell ref="B40:C41"/>
+    <mergeCell ref="A40:A41"/>
+    <mergeCell ref="D40:D41"/>
+    <mergeCell ref="E40:E41"/>
+    <mergeCell ref="F40:F41"/>
+    <mergeCell ref="G40:G41"/>
+    <mergeCell ref="H40:H41"/>
+    <mergeCell ref="I40:I41"/>
+    <mergeCell ref="J40:J41"/>
+    <mergeCell ref="K40:K41"/>
+    <mergeCell ref="B42:C43"/>
+    <mergeCell ref="A42:A43"/>
+    <mergeCell ref="D42:D43"/>
+    <mergeCell ref="E42:E43"/>
+    <mergeCell ref="F42:F43"/>
+    <mergeCell ref="G42:G43"/>
+    <mergeCell ref="H42:H43"/>
+    <mergeCell ref="I42:I43"/>
+    <mergeCell ref="J42:J43"/>
+    <mergeCell ref="K42:K43"/>
+    <mergeCell ref="B44:C45"/>
+    <mergeCell ref="A44:A45"/>
+    <mergeCell ref="D44:D45"/>
+    <mergeCell ref="E44:E45"/>
+    <mergeCell ref="F44:F45"/>
+    <mergeCell ref="G44:G45"/>
+    <mergeCell ref="H44:H45"/>
+    <mergeCell ref="I44:I45"/>
+    <mergeCell ref="J44:J45"/>
+    <mergeCell ref="K44:K45"/>
+    <mergeCell ref="B46:C47"/>
+    <mergeCell ref="A46:A47"/>
+    <mergeCell ref="D46:D47"/>
+    <mergeCell ref="E46:E47"/>
+    <mergeCell ref="F46:F47"/>
+    <mergeCell ref="G46:G47"/>
+    <mergeCell ref="H46:H47"/>
+    <mergeCell ref="I46:I47"/>
+    <mergeCell ref="J46:J47"/>
+    <mergeCell ref="K46:K47"/>
+    <mergeCell ref="A48:J49"/>
+    <mergeCell ref="K48:K49"/>
+    <mergeCell ref="B50:D51"/>
+    <mergeCell ref="A50:A51"/>
+    <mergeCell ref="E50:E51"/>
+    <mergeCell ref="F50:F51"/>
+    <mergeCell ref="G50:G51"/>
+    <mergeCell ref="H50:H51"/>
+    <mergeCell ref="I50:I51"/>
+    <mergeCell ref="J50:J51"/>
+    <mergeCell ref="K50:K51"/>
+    <mergeCell ref="B52:D53"/>
+    <mergeCell ref="A52:A53"/>
+    <mergeCell ref="E52:E53"/>
+    <mergeCell ref="F52:F53"/>
+    <mergeCell ref="G52:G53"/>
+    <mergeCell ref="H52:H53"/>
+    <mergeCell ref="I52:I53"/>
+    <mergeCell ref="J52:J53"/>
+    <mergeCell ref="K52:K53"/>
+    <mergeCell ref="B54:D55"/>
+    <mergeCell ref="A54:A55"/>
+    <mergeCell ref="E54:E55"/>
+    <mergeCell ref="F54:F55"/>
+    <mergeCell ref="G54:G55"/>
+    <mergeCell ref="H54:H55"/>
+    <mergeCell ref="I54:I55"/>
+    <mergeCell ref="J54:J55"/>
+    <mergeCell ref="K54:K55"/>
+    <mergeCell ref="B56:D57"/>
+    <mergeCell ref="A56:A57"/>
+    <mergeCell ref="E56:E57"/>
+    <mergeCell ref="F56:F57"/>
+    <mergeCell ref="G56:G57"/>
+    <mergeCell ref="H56:H57"/>
+    <mergeCell ref="I56:I57"/>
+    <mergeCell ref="J56:J57"/>
+    <mergeCell ref="K56:K57"/>
+    <mergeCell ref="B58:D59"/>
+    <mergeCell ref="A58:A59"/>
+    <mergeCell ref="E58:E59"/>
+    <mergeCell ref="F58:F59"/>
+    <mergeCell ref="G58:G59"/>
+    <mergeCell ref="H58:H59"/>
+    <mergeCell ref="I58:I59"/>
+    <mergeCell ref="J58:J59"/>
+    <mergeCell ref="K58:K59"/>
+    <mergeCell ref="B60:D61"/>
+    <mergeCell ref="A60:A61"/>
+    <mergeCell ref="E60:E61"/>
+    <mergeCell ref="F60:F61"/>
+    <mergeCell ref="G60:G61"/>
+    <mergeCell ref="H60:H61"/>
+    <mergeCell ref="I60:I61"/>
+    <mergeCell ref="J60:J61"/>
+    <mergeCell ref="K60:K61"/>
+    <mergeCell ref="B62:D63"/>
+    <mergeCell ref="A62:A63"/>
+    <mergeCell ref="E62:E63"/>
+    <mergeCell ref="F62:F63"/>
+    <mergeCell ref="G62:G63"/>
+    <mergeCell ref="H62:H63"/>
+    <mergeCell ref="I62:I63"/>
+    <mergeCell ref="J62:J63"/>
+    <mergeCell ref="K62:K63"/>
+    <mergeCell ref="A64:J65"/>
+    <mergeCell ref="K64:K65"/>
+    <mergeCell ref="A66:B75"/>
+    <mergeCell ref="C66:H75"/>
+    <mergeCell ref="I66:J67"/>
+    <mergeCell ref="K66:K67"/>
+    <mergeCell ref="I68:J69"/>
+    <mergeCell ref="K68:K69"/>
+    <mergeCell ref="I70:J71"/>
+    <mergeCell ref="K70:K71"/>
+    <mergeCell ref="I72:J73"/>
+    <mergeCell ref="K72:K73"/>
+    <mergeCell ref="I74:J75"/>
+    <mergeCell ref="K74:K75"/>
+    <mergeCell ref="A76:K77"/>
+    <mergeCell ref="A78:E85"/>
+    <mergeCell ref="F78:K85"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>

--- a/Result_Update_Layout.xlsx
+++ b/Result_Update_Layout.xlsx
@@ -33,8 +33,8 @@
   </si>
   <si>
     <t xml:space="preserve">โปรเจค : โซลาร์เซลล์ 10k 1เฟส 
-          กำลังไฟสูงสุด ( 10.00kWp ) 
-          INVERTER : HUAWEI 
+      กำลังไฟสูงสุด ( 10.00kWp ) 
+      INVERTER : HUAWEI 
  วันที่ : 13 / 5 / 2568 
  เลขที่เอกสาร : PNMMA25016</t>
   </si>
@@ -287,9 +287,9 @@
     <t>สองแสนสี่หมื่นสี่พันบาทถ้วน</t>
   </si>
   <si>
-    <t xml:space="preserve">ลงชื่อผู้ให้บริการ
-___________________
-วันที่ 13 / 5 / 2568</t>
+    <t xml:space="preserve">                                   ลงชื่อผู้ให้บริการ
+                                   ___________________
+                                   วันที่ 13 / 5 / 2568</t>
   </si>
   <si>
     <t xml:space="preserve">ลงชื่อลูกค้า
@@ -456,6 +456,94 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="1" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:oneCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>10000</xdr:colOff>
+      <xdr:row>78</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="2190750" cy="904875"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2454,5 +2542,6 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/Result_Update_Layout.xlsx
+++ b/Result_Update_Layout.xlsx
@@ -504,14 +504,19 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:oneCellAnchor editAs="oneCell">
+  <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>10000</xdr:colOff>
-      <xdr:row>78</xdr:row>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>70000</xdr:colOff>
+      <xdr:row>1</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="2190750" cy="904875"/>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="2" name="Picture 2">
@@ -527,6 +532,45 @@
       </xdr:nvPicPr>
       <xdr:blipFill>
         <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:oneCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>10000</xdr:colOff>
+      <xdr:row>78</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="2190750" cy="904875"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
